--- a/3-能力管理/运行记录类文件/030204-2025年1-10月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/030204-2025年1-10月运维服务能力改进计划及跟踪.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>2025年1-8月运维服务能力改进计划及跟踪</t>
   </si>
@@ -42,9 +42,6 @@
   </si>
   <si>
     <t>改进结果跟踪</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
   <si>
     <t>待改进过程/活动</t>
@@ -99,6 +96,55 @@
   </si>
   <si>
     <t>薛成攀</t>
+  </si>
+  <si>
+    <t>最终软件库考核指标</t>
+  </si>
+  <si>
+    <t>最终软件库</t>
+  </si>
+  <si>
+    <t>最终软件库考核指标不满足</t>
+  </si>
+  <si>
+    <r>
+      <t>1.通过制定标准操作流程与组织强化培训，确保团队规范使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Harbor
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>建立软件可用率专项跟踪机制，定期检查与通报，确保改进效果持续落实</t>
+    </r>
+  </si>
+  <si>
+    <t>2025年12月底前完成</t>
+  </si>
+  <si>
+    <t>跟踪中</t>
   </si>
 </sst>
 </file>
@@ -111,7 +157,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,11 +181,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -283,6 +328,19 @@
       <name val="Arial"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -478,7 +536,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -496,69 +554,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -664,7 +659,7 @@
     </border>
   </borders>
   <cellStyleXfs count="55">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
@@ -674,20 +669,20 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
@@ -722,7 +717,7 @@
     <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -733,28 +728,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="55">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1109,7 +1092,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="20.8796296296296" customWidth="1"/>
@@ -1120,10 +1103,9 @@
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="12.3796296296296" customWidth="1"/>
     <col min="10" max="10" width="9.75" customWidth="1"/>
-    <col min="11" max="11" width="10.8796296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="41.25" customHeight="1" spans="1:11">
+    <row r="1" ht="41.25" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1136,106 +1118,126 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
     </row>
-    <row r="2" ht="26.25" customHeight="1" spans="1:11">
+    <row r="2" ht="26.25" customHeight="1" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="5" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="3" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" ht="26.25" customHeight="1" spans="1:10">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" ht="26.25" customHeight="1" spans="1:11">
-      <c r="A3" s="3"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" ht="130" customHeight="1" spans="1:11">
+    <row r="4" ht="130" customHeight="1" spans="1:10">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="3" t="s">
+    </row>
+    <row r="5" ht="86.4" spans="1:10">
+      <c r="A5" s="5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="G5" s="11"/>
+      <c r="C5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:K1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="87" orientation="landscape"/>

--- a/3-能力管理/运行记录类文件/030204-2025年1-10月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/030204-2025年1-10月运维服务能力改进计划及跟踪.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>2025年1-8月运维服务能力改进计划及跟踪</t>
   </si>
@@ -145,6 +145,19 @@
   </si>
   <si>
     <t>跟踪中</t>
+  </si>
+  <si>
+    <t>满意度调查报告客户反馈</t>
+  </si>
+  <si>
+    <t>满意度调查</t>
+  </si>
+  <si>
+    <t>满意度调查过程中发现客户对解决问题回复及时率得分较低</t>
+  </si>
+  <si>
+    <t>1.开展响应流程、沟通技巧及时效管理的专项培训，提升团队整体服务能力
+2.管控部加强问题响应全程跟踪与督导，明确各环节责任与时限，并优化内部协同及反馈机制，形成闭环管理</t>
   </si>
 </sst>
 </file>
@@ -717,7 +730,7 @@
     <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -737,6 +750,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="55">
@@ -1092,10 +1108,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="2" max="2" width="20.8796296296296" customWidth="1"/>
+    <col min="2" max="2" width="25.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="11.8888888888889" customWidth="1"/>
     <col min="4" max="4" width="17.8796296296296" customWidth="1"/>
     <col min="5" max="5" width="26.6296296296296" customWidth="1"/>
     <col min="6" max="6" width="12.75" customWidth="1"/>
@@ -1221,13 +1238,45 @@
       <c r="G5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="100.8" spans="1:10">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>21</v>
       </c>
     </row>
